--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486264_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486264_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. MARTIN MARIN</t>
+          <t>I. RIVERA CARROLL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8503</v>
+        <v>3.8175</v>
       </c>
       <c r="E2" t="n">
-        <v>1.109</v>
+        <v>-0.5633</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7413</v>
+        <v>4.3808</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8663</v>
+        <v>1.6653</v>
       </c>
       <c r="H2" t="n">
-        <v>3.236</v>
+        <v>0.9944</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6303</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4966</v>
+        <v>0.0878</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5914</v>
+        <v>1.4631</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.0948</v>
+        <v>-1.3754</v>
       </c>
       <c r="M2" t="n">
-        <v>1.3697</v>
+        <v>1.5775</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6446</v>
+        <v>-0.4688</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7251</v>
+        <v>2.0463</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.305</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R2" t="n">
-        <v>0.87</v>
+        <v>2.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8409</v>
+        <v>0.6318</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3425</v>
+        <v>0.0036</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4985</v>
+        <v>0.6282</v>
       </c>
       <c r="V2" t="n">
-        <v>1.13</v>
+        <v>1.5204</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>1.5204</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. RIVERA CARROLL</t>
+          <t>A. MARTIN MARIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7419</v>
+        <v>3.3319</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.7313</v>
+        <v>1.2208</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4732</v>
+        <v>2.1112</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6653</v>
+        <v>3.8663</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9944</v>
+        <v>3.236</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6709000000000001</v>
+        <v>0.6303</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0878</v>
+        <v>2.4966</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4631</v>
+        <v>2.5914</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.3754</v>
+        <v>-0.0948</v>
       </c>
       <c r="M3" t="n">
-        <v>1.5775</v>
+        <v>1.3697</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4688</v>
+        <v>0.6446</v>
       </c>
       <c r="O3" t="n">
-        <v>2.0463</v>
+        <v>0.7251</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>-1.305</v>
       </c>
       <c r="Q3" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1751</v>
+        <v>0.87</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4438</v>
+        <v>-0.3593</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1644</v>
+        <v>-0.2307</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7206</v>
+        <v>-0.1286</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5204</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5204</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4794</v>
+        <v>1.6115</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6619</v>
+        <v>-0.0519</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8175</v>
+        <v>1.6633</v>
       </c>
       <c r="G4" t="n">
         <v>1.0781</v>
@@ -766,13 +766,13 @@
         <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9233</v>
+        <v>1.0554</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5502</v>
+        <v>0.8364</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3731</v>
+        <v>0.219</v>
       </c>
       <c r="V4" t="n">
         <v>-0.7395</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. FAVERANI TATSCH</t>
+          <t>S. SVEJCAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5258</v>
+        <v>0.6807</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.832</v>
+        <v>1.8489</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3579</v>
+        <v>-1.1682</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6306</v>
+        <v>0.2433</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9612000000000001</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6694</v>
+        <v>0.8335</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6738</v>
+        <v>1.2165</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4115</v>
+        <v>0.2587</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2622</v>
+        <v>0.9578</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0432</v>
+        <v>-0.9732</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4504</v>
+        <v>-0.8488</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4072</v>
+        <v>-0.1243</v>
       </c>
       <c r="P5" t="n">
-        <v>-4.1326</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.4377</v>
+        <v>-2.1751</v>
       </c>
       <c r="R5" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9626</v>
+        <v>-0.17</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7367</v>
+        <v>-0.2127</v>
       </c>
       <c r="U5" t="n">
-        <v>2.226</v>
+        <v>0.0427</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9347</v>
+        <v>1.695</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1952</v>
+        <v>3.0202</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. SUOKAS</t>
+          <t>A. DOMENECH FONTANA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1243</v>
+        <v>0.5627</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4101</v>
+        <v>-2.4994</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2858</v>
+        <v>3.0621</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.1888</v>
+        <v>-0.8583</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1125</v>
+        <v>0.0636</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.3013</v>
+        <v>-0.922</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5759</v>
+        <v>-1.4287</v>
       </c>
       <c r="K6" t="n">
-        <v>0.876</v>
+        <v>0.73</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4519</v>
+        <v>-2.1587</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6129</v>
+        <v>0.5704</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7635</v>
+        <v>-0.6663</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8495</v>
+        <v>1.2367</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2175</v>
+        <v>1.9576</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1644</v>
+        <v>0.551</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.274</v>
+        <v>0.0168</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1096</v>
+        <v>0.5341</v>
       </c>
       <c r="V6" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DOMENECH FONTANA</t>
+          <t>T. SUOKAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0374</v>
+        <v>0.5464</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.5931</v>
+        <v>1.7706</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6305</v>
+        <v>-1.2242</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8583</v>
+        <v>-2.1888</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0636</v>
+        <v>0.1125</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.922</v>
+        <v>-2.3013</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.4287</v>
+        <v>-0.5759</v>
       </c>
       <c r="K7" t="n">
-        <v>0.73</v>
+        <v>0.876</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.1587</v>
+        <v>-1.4519</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5704</v>
+        <v>-1.6129</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6663</v>
+        <v>-0.7635</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2367</v>
+        <v>-0.8495</v>
       </c>
       <c r="P7" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9576</v>
+        <v>0.2175</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0257</v>
+        <v>0.2578</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0769</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1026</v>
+        <v>0.1712</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. SVEJCAR</t>
+          <t>V. FAVERANI TATSCH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2916</v>
+        <v>-1.0921</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3081</v>
+        <v>-2.3404</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5997</v>
+        <v>1.2482</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2433</v>
+        <v>2.6306</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5901999999999999</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8335</v>
+        <v>1.6694</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2165</v>
+        <v>2.6738</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2587</v>
+        <v>1.4115</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9578</v>
+        <v>1.2622</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9732</v>
+        <v>-0.0432</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8488</v>
+        <v>-0.4504</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1243</v>
+        <v>0.4072</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.0875</v>
+        <v>-4.1326</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1751</v>
+        <v>-5.4377</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1423</v>
+        <v>1.3447</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.2283</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3889</v>
+        <v>1.1164</v>
       </c>
       <c r="V8" t="n">
-        <v>1.695</v>
+        <v>-0.9347</v>
       </c>
       <c r="W8" t="n">
-        <v>3.0202</v>
+        <v>0.1952</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. HARGUINDEY MANEIRO</t>
+          <t>A. KELLY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5592</v>
+        <v>-1.2347</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1213</v>
+        <v>0.2593</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4379</v>
+        <v>-1.494</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2987</v>
+        <v>-0.9379</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2525</v>
+        <v>-0.9945000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0462</v>
+        <v>0.0566</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5142</v>
+        <v>-0.2812</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3285</v>
+        <v>-0.7601</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1857</v>
+        <v>0.4789</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8129</v>
+        <v>-0.6567</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.581</v>
+        <v>-0.2344</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.232</v>
+        <v>-0.4224</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7401</v>
+        <v>-0.435</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4796</v>
+        <v>0.3335</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5396</v>
+        <v>0.3028</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.06</v>
+        <v>0.0306</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. GARUBA ALARI</t>
+          <t>A. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8388</v>
+        <v>-1.6833</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2213</v>
+        <v>-0.2763</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3825</v>
+        <v>-1.407</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3936</v>
+        <v>-0.2987</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5872</v>
+        <v>-0.2525</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1936</v>
+        <v>-0.0462</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0979</v>
+        <v>1.5142</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3529</v>
+        <v>0.3285</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7451</v>
+        <v>1.1857</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7043</v>
+        <v>-1.8129</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2344</v>
+        <v>-0.581</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9387</v>
+        <v>-1.232</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.8276</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.3501</v>
+        <v>-2.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="S10" t="n">
-        <v>2.5776</v>
+        <v>0.3554</v>
       </c>
       <c r="T10" t="n">
-        <v>2.2268</v>
+        <v>0.3845</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3509</v>
+        <v>-0.0291</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. KELLY</t>
+          <t>A. GARUBA ALARI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8458</v>
+        <v>-2.923</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.66</v>
+        <v>-5.3569</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1858</v>
+        <v>2.4339</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9379</v>
+        <v>-1.3936</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9945000000000001</v>
+        <v>-1.5872</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0566</v>
+        <v>0.1936</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2812</v>
+        <v>-2.0979</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7601</v>
+        <v>-1.3529</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4789</v>
+        <v>-0.7451</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6567</v>
+        <v>0.7043</v>
       </c>
       <c r="N11" t="n">
         <v>-0.2344</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4224</v>
+        <v>0.9387</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.435</v>
+        <v>-2.8276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0875</v>
+        <v>-4.3501</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2776</v>
+        <v>1.4934</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6165</v>
+        <v>1.0911</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3389</v>
+        <v>0.4023</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1952</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5204</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.5357</v>
+        <v>-4.1655</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.256</v>
+        <v>-6.2249</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7203</v>
+        <v>2.0594</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6905</v>
@@ -1390,13 +1390,13 @@
         <v>1.5225</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.93</v>
+        <v>0.4401</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.822</v>
+        <v>0.2091</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.108</v>
+        <v>0.231</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.312</v>
+        <v>-0.5479000000000012</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.9259</v>
+        <v>-12.2135</v>
       </c>
       <c r="F13" t="n">
-        <v>11.614</v>
+        <v>11.6655</v>
       </c>
       <c r="G13" t="n">
         <v>3.115799999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>1.824900000000001</v>
+        <v>1.8249</v>
       </c>
       <c r="I13" t="n">
         <v>1.2908</v>
@@ -1450,7 +1450,7 @@
         <v>-2.7812</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4319000000000002</v>
+        <v>-0.4319000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>-4.5037</v>
@@ -1468,16 +1468,16 @@
         <v>13.0502</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1698</v>
+        <v>5.933800000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0035</v>
+        <v>2.7157</v>
       </c>
       <c r="U13" t="n">
-        <v>3.1663</v>
+        <v>3.2178</v>
       </c>
       <c r="V13" t="n">
-        <v>4.540700000000001</v>
+        <v>4.5407</v>
       </c>
       <c r="W13" t="n">
         <v>8.711399999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5099</v>
+        <v>4.7624</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.5905</v>
       </c>
       <c r="F14" t="n">
-        <v>4.6959</v>
+        <v>4.1719</v>
       </c>
       <c r="G14" t="n">
         <v>2.8775</v>
@@ -1546,13 +1546,13 @@
         <v>4.1326</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0429</v>
+        <v>-0.7904</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8304</v>
+        <v>-1.0539</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7875</v>
+        <v>0.2635</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3698</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3484</v>
+        <v>1.1981</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0837</v>
+        <v>-0.2516</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2647</v>
+        <v>1.4496</v>
       </c>
       <c r="G15" t="n">
         <v>1.1917</v>
@@ -1624,13 +1624,13 @@
         <v>4.5676</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1711</v>
+        <v>-0.3214</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1322</v>
+        <v>-0.2031</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3033</v>
+        <v>-0.1184</v>
       </c>
       <c r="V15" t="n">
         <v>-2.0647</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MARTINEZ CABEZUDO</t>
+          <t>L. BRACEY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9756</v>
+        <v>0.8676</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5993000000000001</v>
+        <v>-0.8472</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3763</v>
+        <v>1.7148</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3963</v>
+        <v>1.1973</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0122</v>
+        <v>-2.579</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3841</v>
+        <v>3.7763</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6642</v>
+        <v>0.5895</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0251</v>
+        <v>-1.9948</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3609</v>
+        <v>2.5843</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2679</v>
+        <v>0.6078</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0129</v>
+        <v>-0.5843</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7451</v>
+        <v>1.1921</v>
       </c>
       <c r="P16" t="n">
-        <v>0.435</v>
+        <v>3.0451</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5225</v>
+        <v>4.1326</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2743</v>
+        <v>-1.1149</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0227</v>
+        <v>-0.5444</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2516</v>
+        <v>-0.5705</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.13</v>
+        <v>-2.2599</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.13</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ARAMBURU LAMY</t>
+          <t>B. VAZQUEZ ARRAIZA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5794</v>
+        <v>0.7791</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.0734</v>
+        <v>-1.5933</v>
       </c>
       <c r="F17" t="n">
-        <v>3.6528</v>
+        <v>2.3725</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0064</v>
+        <v>-3.4374</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0462</v>
+        <v>-2.5091</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0399</v>
+        <v>-0.9283</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.1312</v>
+        <v>-2.1861</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0635</v>
+        <v>-1.2132</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.0678</v>
+        <v>-0.9729</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1249</v>
+        <v>-1.2512</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9827</v>
+        <v>-1.2959</v>
       </c>
       <c r="O17" t="n">
-        <v>1.1076</v>
+        <v>0.0446</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6525</v>
+        <v>3.2626</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.9151</v>
+        <v>3.2626</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5635</v>
+        <v>-0.3506</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0048</v>
+        <v>-0.5371</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5683</v>
+        <v>0.1866</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3698</v>
+        <v>1.3045</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3252</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.9554</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. BRACEY</t>
+          <t>J. MARTINEZ CABEZUDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5285</v>
+        <v>0.4554</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8472</v>
+        <v>0.264</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3757</v>
+        <v>0.1914</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1973</v>
+        <v>0.3963</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.579</v>
+        <v>0.0122</v>
       </c>
       <c r="I18" t="n">
-        <v>3.7763</v>
+        <v>0.3841</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5895</v>
+        <v>0.6642</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.9948</v>
+        <v>1.0251</v>
       </c>
       <c r="L18" t="n">
-        <v>2.5843</v>
+        <v>-0.3609</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6078</v>
+        <v>-0.2679</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5843</v>
+        <v>-1.0129</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1921</v>
+        <v>0.7451</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0451</v>
+        <v>0.435</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>4.1326</v>
+        <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4539</v>
+        <v>0.7541</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5444</v>
+        <v>0.6874</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9096</v>
+        <v>0.0667</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.2599</v>
+        <v>-1.13</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.4552</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. VAZQUEZ ARRAIZA</t>
+          <t>J. ARAMBURU LAMY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0046</v>
+        <v>0.0168</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1521</v>
+        <v>-3.297</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1567</v>
+        <v>3.3138</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.4374</v>
+        <v>-1.0064</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.5091</v>
+        <v>-1.0462</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9283</v>
+        <v>0.0399</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.1861</v>
+        <v>-1.1312</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2132</v>
+        <v>-0.0635</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.9729</v>
+        <v>-1.0678</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2512</v>
+        <v>0.1249</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2959</v>
+        <v>-0.9827</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0446</v>
+        <v>1.1076</v>
       </c>
       <c r="P19" t="n">
-        <v>3.2626</v>
+        <v>0.6525</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R19" t="n">
-        <v>3.2626</v>
+        <v>3.9151</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1251</v>
+        <v>0.0009</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0959</v>
+        <v>-0.2283</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0292</v>
+        <v>0.2292</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3045</v>
+        <v>0.3698</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>1.3252</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1745</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3075</v>
+        <v>-0.1033</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2877</v>
+        <v>-0.176</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0198</v>
+        <v>0.0727</v>
       </c>
       <c r="G20" t="n">
         <v>0.1344</v>
@@ -2014,13 +2014,13 @@
         <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8769</v>
+        <v>-0.6726</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3425</v>
+        <v>-0.2307</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5344</v>
+        <v>-0.4419</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1685</v>
+        <v>-1.1878</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6363</v>
+        <v>-0.7481</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5322</v>
+        <v>-0.4398</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8312</v>
@@ -2092,13 +2092,13 @@
         <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0977</v>
+        <v>0.0784</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2656</v>
+        <v>0.1538</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1679</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9803</v>
+        <v>-1.7066</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6486</v>
+        <v>-2.3133</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6683</v>
+        <v>0.6067</v>
       </c>
       <c r="G22" t="n">
         <v>-2.0299</v>
@@ -2170,13 +2170,13 @@
         <v>1.9576</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6251</v>
+        <v>-0.3515</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.399</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2262</v>
+        <v>-0.2878</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1952</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1784</v>
+        <v>-2.7699</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4658</v>
+        <v>-3.2423</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2874</v>
+        <v>0.4723</v>
       </c>
       <c r="G23" t="n">
         <v>-1.608</v>
@@ -2248,13 +2248,13 @@
         <v>2.6101</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8102</v>
+        <v>-1.4018</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3699</v>
+        <v>-1.1464</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4403</v>
+        <v>-0.2554</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1952</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.3117</v>
+        <v>2.311800000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-11.6141</v>
+        <v>-11.6143</v>
       </c>
       <c r="F24" t="n">
-        <v>13.9258</v>
+        <v>13.9259</v>
       </c>
       <c r="G24" t="n">
         <v>-3.1157</v>
@@ -2311,7 +2311,7 @@
         <v>-3.5477</v>
       </c>
       <c r="N24" t="n">
-        <v>-6.3284</v>
+        <v>-6.328399999999999</v>
       </c>
       <c r="O24" t="n">
         <v>2.781</v>
@@ -2326,13 +2326,13 @@
         <v>27.1882</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.1697</v>
+        <v>-4.1698</v>
       </c>
       <c r="T24" t="n">
         <v>-3.1664</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0035</v>
+        <v>-1.0034</v>
       </c>
       <c r="V24" t="n">
         <v>-4.5405</v>
